--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_271_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_271_R28.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5713</v>
+        <v>10.1502</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4763</v>
+        <v>7.1224</v>
       </c>
       <c r="F2" t="n">
-        <v>3.095</v>
+        <v>3.0278</v>
       </c>
       <c r="G2" t="n">
         <v>9.944000000000001</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7644</v>
+        <v>-1.1854</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1019</v>
+        <v>-0.4558</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6625</v>
+        <v>-0.7297</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2472</v>
+        <v>5.5331</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5181</v>
+        <v>4.636</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7291</v>
+        <v>0.8971</v>
       </c>
       <c r="G3" t="n">
         <v>3.8518</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9088</v>
+        <v>-1.6228</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8136</v>
+        <v>-0.6956</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0952</v>
+        <v>-0.9271</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8352</v>
+        <v>5.2392</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3937</v>
+        <v>2.6296</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4415</v>
+        <v>2.6096</v>
       </c>
       <c r="G4" t="n">
         <v>3.5843</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.981</v>
+        <v>-0.577</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.3727</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.508</v>
+        <v>4.1206</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2613</v>
+        <v>1.9074</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2467</v>
+        <v>2.2131</v>
       </c>
       <c r="G5" t="n">
         <v>4.3506</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0382</v>
+        <v>-0.4257</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0272</v>
+        <v>-0.3811</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.011</v>
+        <v>-0.0446</v>
       </c>
       <c r="V5" t="n">
         <v>-1.8919</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0868</v>
+        <v>1.6281</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6938</v>
+        <v>1.2351</v>
       </c>
       <c r="F6" t="n">
         <v>0.3931</v>
@@ -922,10 +922,10 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5727</v>
+        <v>0.114</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3986</v>
+        <v>0.9399</v>
       </c>
       <c r="U6" t="n">
         <v>-0.8259</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3734</v>
+        <v>1.2921</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7278</v>
+        <v>1.1052</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1012</v>
+        <v>0.1869</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2143</v>
+        <v>4.9071</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1402</v>
+        <v>2.4177</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0741</v>
+        <v>2.4894</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8532</v>
+        <v>3.6132</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.3815</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2882</v>
+        <v>2.2317</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3611</v>
+        <v>1.294</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5752</v>
+        <v>1.0362</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.214</v>
+        <v>0.2578</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0876</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0353</v>
+        <v>-0.4011</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6869</v>
+        <v>-0.1885</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3484</v>
+        <v>-0.2126</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7886</v>
+        <v>-2.2862</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3752</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3228</v>
+        <v>-1.6723</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0524</v>
+        <v>2.2141</v>
       </c>
       <c r="G8" t="n">
-        <v>4.9071</v>
+        <v>-0.3968</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4177</v>
+        <v>2.2065</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4894</v>
+        <v>-2.6034</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6132</v>
+        <v>-1.7514</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3815</v>
+        <v>1.2134</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2317</v>
+        <v>-2.9649</v>
       </c>
       <c r="M8" t="n">
-        <v>1.294</v>
+        <v>1.3546</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0362</v>
+        <v>0.9931</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2578</v>
+        <v>0.3615</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3179</v>
+        <v>-0.8268</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9709</v>
+        <v>-0.0626</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.347</v>
+        <v>-0.7641</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2862</v>
+        <v>0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.056</v>
+        <v>0.202</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5726</v>
+        <v>-1.5967</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5166</v>
+        <v>1.7987</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3968</v>
+        <v>2.2143</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2065</v>
+        <v>1.1402</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6034</v>
+        <v>1.0741</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7514</v>
+        <v>1.8532</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2134</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.9649</v>
+        <v>1.2882</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3546</v>
+        <v>0.3611</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9931</v>
+        <v>0.5752</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3615</v>
+        <v>-0.214</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6237</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4246</v>
+        <v>0.8639</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.963</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4617</v>
+        <v>0.0459</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6131</v>
+        <v>-0.2763</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7508</v>
+        <v>-0.5149</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1378</v>
+        <v>0.2386</v>
       </c>
       <c r="G10" t="n">
         <v>0.7838000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7859</v>
+        <v>-0.4492</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1138</v>
+        <v>-0.013</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0026</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8074</v>
+        <v>-0.5367</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6634</v>
+        <v>-2.5272</v>
       </c>
       <c r="F11" t="n">
-        <v>1.856</v>
+        <v>1.9905</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7135</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5578</v>
+        <v>-0.2871</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8215</v>
+        <v>0.3148</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7363</v>
+        <v>-0.6018</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>27.5206</v>
+        <v>27.8941</v>
       </c>
       <c r="E12" t="n">
-        <v>11.9514</v>
+        <v>12.3246</v>
       </c>
       <c r="F12" t="n">
-        <v>15.5694</v>
+        <v>15.5695</v>
       </c>
       <c r="G12" t="n">
         <v>28.4135</v>
@@ -1390,16 +1390,16 @@
         <v>13.9173</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.170600000000001</v>
+        <v>-4.7972</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7249000000000003</v>
+        <v>-0.3514000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.4458</v>
+        <v>-4.4456</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6805</v>
+        <v>-2.680499999999999</v>
       </c>
       <c r="W12" t="n">
         <v>4.856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3295</v>
+        <v>1.32</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7378</v>
+        <v>0.266</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5917</v>
+        <v>1.054</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3758</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1693</v>
+        <v>1.1598</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3135</v>
+        <v>0.8417</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8558</v>
+        <v>0.3181</v>
       </c>
       <c r="V13" t="n">
         <v>1.6083</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7334</v>
+        <v>0.5938</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1048</v>
+        <v>1.0432</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3714</v>
+        <v>-0.4494</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5226</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1864</v>
+        <v>1.0468</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7774</v>
+        <v>0.7158</v>
       </c>
       <c r="U14" t="n">
-        <v>0.409</v>
+        <v>0.331</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4427</v>
+        <v>-0.3398</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3286</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8859</v>
+        <v>-1.1799</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0672</v>
+        <v>-0.5403</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3085</v>
+        <v>-0.6541</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.3757</v>
+        <v>0.1138</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.959</v>
+        <v>0.6393</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0454</v>
+        <v>0.0504</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.0044</v>
+        <v>0.5889</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1082</v>
+        <v>-1.1796</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7369</v>
+        <v>-0.7045</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3713</v>
+        <v>-0.4751</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9918</v>
+        <v>-0.0314</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2334</v>
+        <v>0.0591</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2416</v>
+        <v>-0.0905</v>
       </c>
       <c r="V15" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.214</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0206</v>
+        <v>-0.3783</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7297</v>
+        <v>1.14</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7091</v>
+        <v>-1.5182</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3425</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3631</v>
+        <v>0.9643</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1246</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2385</v>
+        <v>0.4294</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1204</v>
+        <v>-0.804</v>
       </c>
       <c r="E17" t="n">
-        <v>1.194</v>
+        <v>0.1491</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3144</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5403</v>
+        <v>-2.0672</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6541</v>
+        <v>0.3085</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1138</v>
+        <v>-2.3757</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6393</v>
+        <v>-0.959</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0504</v>
+        <v>1.0454</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5889</v>
+        <v>-2.0044</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1796</v>
+        <v>-1.1082</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7045</v>
+        <v>-0.7369</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4751</v>
+        <v>-0.3713</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.188</v>
+        <v>0.7451</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4129</v>
+        <v>1.0539</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2249</v>
+        <v>-0.3088</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4407</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8053</v>
+        <v>-0.2155</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6355</v>
+        <v>-0.7699</v>
       </c>
       <c r="G18" t="n">
         <v>-0.204</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1344</v>
+        <v>0.5898</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2636</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1291</v>
+        <v>-0.2636</v>
       </c>
       <c r="V18" t="n">
         <v>0.2525</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4862</v>
+        <v>-1.1494</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.043</v>
+        <v>0.1929</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4431</v>
+        <v>-1.3423</v>
       </c>
       <c r="G19" t="n">
         <v>-0.721</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0751</v>
+        <v>0.4118</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3655</v>
+        <v>-0.1296</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4406</v>
+        <v>0.5414</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4306</v>
+        <v>-3.0308</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8679</v>
+        <v>0.1903</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5627</v>
+        <v>-3.2211</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.333</v>
+        <v>-1.8044</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3025</v>
+        <v>0.521</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0305</v>
+        <v>-2.3254</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9613</v>
+        <v>-0.2926</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2486</v>
+        <v>1.1329</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7127</v>
+        <v>-1.4255</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3717</v>
+        <v>-1.5119</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0539</v>
+        <v>-0.612</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3178</v>
+        <v>-0.8999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3295</v>
+        <v>-0.1542</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7468</v>
+        <v>0.5704</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4173</v>
+        <v>-0.7246</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6193</v>
+        <v>-3.3291</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8713</v>
+        <v>-2.632</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.7481</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8044</v>
+        <v>-1.333</v>
       </c>
       <c r="H21" t="n">
-        <v>0.521</v>
+        <v>-0.3025</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3254</v>
+        <v>-1.0305</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2926</v>
+        <v>-0.9613</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1329</v>
+        <v>-0.2486</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4255</v>
+        <v>-0.7127</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5119</v>
+        <v>-0.3717</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.612</v>
+        <v>-0.0539</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8999</v>
+        <v>-0.3178</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7427</v>
+        <v>-0.228</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4911</v>
+        <v>-0.5109</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2516</v>
+        <v>0.2829</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7105</v>
+        <v>-4.0649</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9026</v>
+        <v>-3.5488</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8079</v>
+        <v>-0.5162</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8574</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1265</v>
+        <v>0.519</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3339</v>
+        <v>0.02</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2074</v>
+        <v>0.4991</v>
       </c>
       <c r="V22" t="n">
         <v>2.6805</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8614</v>
+        <v>-4.6261</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9386</v>
+        <v>-3.995</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9228</v>
+        <v>-0.6311</v>
       </c>
       <c r="G23" t="n">
         <v>-5.495</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8303</v>
+        <v>0.405</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1949</v>
+        <v>-0.2513</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3646</v>
+        <v>0.6563</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.378</v>
+        <v>-9.9405</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.2357</v>
+        <v>-8.9998</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1423</v>
+        <v>-0.9406</v>
       </c>
       <c r="G24" t="n">
         <v>-8.149900000000001</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0914</v>
+        <v>0.5289</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4525</v>
+        <v>0.6884</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3611</v>
+        <v>-0.1595</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-27.5209</v>
+        <v>-26.7345</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.5695</v>
+        <v>-15.5694</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.9515</v>
+        <v>-11.1649</v>
       </c>
       <c r="G25" t="n">
         <v>-28.4131</v>
@@ -2383,7 +2383,7 @@
         <v>-6.3224</v>
       </c>
       <c r="L25" t="n">
-        <v>-7.311900000000001</v>
+        <v>-7.3119</v>
       </c>
       <c r="M25" t="n">
         <v>-14.7788</v>
@@ -2404,16 +2404,16 @@
         <v>6.958799999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>5.170499999999999</v>
+        <v>5.956900000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>4.4457</v>
+        <v>4.4456</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7248999999999999</v>
+        <v>1.5112</v>
       </c>
       <c r="V25" t="n">
-        <v>2.6805</v>
+        <v>2.680499999999999</v>
       </c>
       <c r="W25" t="n">
         <v>7.5365</v>
